--- a/Dokumente/Sammelobjekte im Projekt Dhampir.xlsx
+++ b/Dokumente/Sammelobjekte im Projekt Dhampir.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dokumente\1. Projekte\Dhampir\Dokumente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A000350F-7A83-4633-BB52-98CA9919E529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD202CE6-6025-44EC-888F-BDE8D6EB564D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="139">
   <si>
     <t>Inhalt</t>
   </si>
@@ -66,22 +66,7 @@
     <t>Nordamerika</t>
   </si>
   <si>
-    <t>In dieser Generation pflanzten 
-man sich durch Bluttransfer 
-fort</t>
-  </si>
-  <si>
-    <t>In dieser Generation kam 
-es zu keiner Fortpflanzung</t>
-  </si>
-  <si>
     <t>Als Sperre gegen ihren Seelendurst werden Sie mit "Re's Fluch" belegt wo durch sie bei Berührung mit dem Sonnenlicht zu Wüstensand werden.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">700 u.Z.: Durch dunke Magie kommt es zur Erschaffung von Urvampiren durch eine Hexe aus Sibirien, um Rache an ihren Verfolgern zu nehmen. </t>
-  </si>
-  <si>
-    <t>1000 u.Z.: Durch dunke Magie kommt es zur Erschaffung von Urvampiren durch eine Hexe aus Skandinavien, um ihre Nachkommen vor Werwölfen zu beschützen.</t>
   </si>
   <si>
     <t xml:space="preserve">5.100 v.u.Z.: Durch dunkle Rituale werden die Urvampire als mit Feuerkräften gesegnete Krieger 
@@ -159,16 +144,9 @@
     </r>
   </si>
   <si>
-    <t>11.000 v.u.Z.: Eine unbekannte hochentwickelte Spezies, verwandelt nach einem Angriff eines feindlichen Reiches, einen Teil ihrer Krieger in Monster mit Kräften, die Sie ihnen mit Hilfe von Meteoritengestein weitergaben.</t>
-  </si>
-  <si>
     <t>7.800 v.u.Z.: Eine unbekannte hochentwickelte Spezies, verwandelt nach einem Aufstand ihrer Sklaven in Doggerland, Teile ihrer Palastwache in fledermaushafte Krieger. Diese verstärken ihre Sinne, ihre Agilität und erhalten unterschiedliche Mutationskräfte.</t>
   </si>
   <si>
-    <t>In dieser Generation pflanzten 
-man sich durch Paarung fort</t>
-  </si>
-  <si>
     <t>Um ihren Blutdurst zu bremsen, wurde ihnen eine Abneigung gegen grelles Sonnenlicht auferlegt, bei dem sich ihre Haut zu Kristallen schmerzhaft verkrustet. (heilt sich durch Dunkelheit)</t>
   </si>
   <si>
@@ -181,45 +159,12 @@
     <t>Die Clans der Werwölfe</t>
   </si>
   <si>
-    <t>Die Wervölker</t>
-  </si>
-  <si>
     <t>Nur noch einer übrig</t>
   </si>
   <si>
-    <t>Die Werbärin</t>
-  </si>
-  <si>
-    <t>Die Werfüchse</t>
-  </si>
-  <si>
-    <t>Die Werjackale</t>
-  </si>
-  <si>
-    <t>Die Werraten</t>
-  </si>
-  <si>
-    <t>Nur noch zwei Männliche</t>
-  </si>
-  <si>
-    <t>Der Púca (Werziege)</t>
-  </si>
-  <si>
-    <t>Die Werfalken</t>
-  </si>
-  <si>
-    <t>Die Werkrähen</t>
-  </si>
-  <si>
-    <t>Die Wereulen</t>
-  </si>
-  <si>
     <t>Die Sirenen</t>
   </si>
   <si>
-    <t>Die Werkatzen</t>
-  </si>
-  <si>
     <t>Die Drachen</t>
   </si>
   <si>
@@ -241,34 +186,10 @@
     <t>Die Grünen Magier</t>
   </si>
   <si>
-    <t>Die Dunklen Magier</t>
-  </si>
-  <si>
     <t>Die Zeitmagier</t>
   </si>
   <si>
-    <t>Die Blutmagier (Seelenmagier)</t>
-  </si>
-  <si>
-    <t>Dämonen</t>
-  </si>
-  <si>
-    <t>Die Emotionsmagier</t>
-  </si>
-  <si>
-    <t>Die Lichtmagier (Leben)</t>
-  </si>
-  <si>
-    <t>Der Einsame</t>
-  </si>
-  <si>
-    <t>Druidentum</t>
-  </si>
-  <si>
     <t>Grenzen</t>
-  </si>
-  <si>
-    <t>Volk</t>
   </si>
   <si>
     <t>Hexer</t>
@@ -278,21 +199,522 @@
 andere Werwesen zu erschaffen. Als natürlichen Feind der Vampire erschufen Sie den Werwolf.</t>
   </si>
   <si>
+    <t>Sammelobjekte in Dhampir</t>
+  </si>
+  <si>
+    <t>Die Urvölker</t>
+  </si>
+  <si>
+    <t>Die Banshee</t>
+  </si>
+  <si>
+    <t>Urvolk</t>
+  </si>
+  <si>
+    <t>Die Clans der Werwesen der Lüfte</t>
+  </si>
+  <si>
+    <t>Die Clans der Werwesen der Meere</t>
+  </si>
+  <si>
+    <t>Die Clans der Werwesen der Berge</t>
+  </si>
+  <si>
+    <t>Europa</t>
+  </si>
+  <si>
+    <t>1500 EP</t>
+  </si>
+  <si>
+    <t>10.500 v.u.Z.: Das unbekannte hochentwickelte Volk was die ersten Urvampire erschuf, erlang die Macht
+andere Werwesen zu erschaffen. Als Unterstützung gegen die Werwesen erschufen Sie die Banshees.</t>
+  </si>
+  <si>
+    <t>10.500 v.u.Z.: Das unbekannte hochentwickelte Volk was die ersten Urvampire erschuf, erlang die Macht
+andere Werwesen zu erschaffen. Als Unterstützung für die Tiere der Natur erschuf man den Pucca.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Doggerland
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>untergegangen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 
+&gt; Heute Europa</t>
+    </r>
+  </si>
+  <si>
+    <t>Nur noch wenige in Europa 
+übrig, in Irland ist eine gut aufgebaute Gemeinschaft</t>
+  </si>
+  <si>
+    <t>Durch Spezialrüstung und/oder Unterbrechung mit Magie und Kugeln 
+lassen Sie sich besiegen.</t>
+  </si>
+  <si>
+    <t>Beringia</t>
+  </si>
+  <si>
+    <t>500 EP</t>
+  </si>
+  <si>
+    <t>Vergessene und
+Untergegangene Reiche</t>
+  </si>
+  <si>
+    <t>Beringia ist der Name für die Region zwischen Ostsibirien und Alaska, die während des Pleistozäns
+mehrfach durch Rückgang des globalen Meeresspiegels trocken fiel und zudem eisfrei war. Hier bildete
+sich das erste Königreich einer Menschen ähnlichen Spezies, die sich auf die Forschung spezialisierte.</t>
+  </si>
+  <si>
+    <t>Doggerland</t>
+  </si>
+  <si>
+    <t>Doggerland war eine Landmasse, die während der letzten Eiszeit zwischen Großbritannien und dem europäischen Festland lag und heute von der Nordsee bedeckt ist. Es war ein fruchtbares Gebiet, das von Jägern und Sammlern der Mittelsteinzeit besiedelt wurde und durch den Anstieg des Meeresspiegels vor etwa 8.200 Jahren überflutet wurde. Heute zeugen Funde wie Werkzeuge und Knochen sowie die Reste
+von Helgoland und den Halligen von diesem versunkenen Land. Nach dem Untergang von dem Reich auf Beringia bildete Sich die Gesellschaft der Forschung weiter aus.</t>
+  </si>
+  <si>
+    <t>Gründe des Untergang</t>
+  </si>
+  <si>
+    <t>Reich von Akkad</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mesopotanien
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>teilweise untergegangen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Das Reich von Akkad in Mesopotamien, benannt nach seiner Hauptstadt Akkad, existierte im 24. und 23. Jh. v.u.Z. rund 150 Jahre lang und gilt als erster Flächenstaat der Menschheitsgeschichte. Mit seiner Errichtung wurde zudem erstmals eine semitische Sprache zur offiziellen Sprache eines Staates. Überreste der Ersten Vampire und Werwölfe rotteten Sich in den Staatsaufbau.</t>
+  </si>
+  <si>
+    <t>Klilmawandel &gt; Sintflut</t>
+  </si>
+  <si>
+    <t>Römisches Reich</t>
+  </si>
+  <si>
+    <t>Völkerwanderung und Aufbegehren der Urvölker</t>
+  </si>
+  <si>
+    <t>Perserreich</t>
+  </si>
+  <si>
+    <t>Eurasien, Afrika</t>
+  </si>
+  <si>
+    <t>Das Römische Reich war das von den Römern, der Stadt Rom bzw. dem römischen Staat beherrschte 
+Gebiet zwischen dem 8. Jh. v.u.Z. und 7. Jh. n.u.Z.. Von Werwölf Clans gegründet, hatte dieses Reich mit 
+Kämpfen gegen andere Urvölker und Hexenwesen zu kämpfen, die Schlussendlich mit Völkerbewegung 
+zum Untergang des Imperiums führten.</t>
+  </si>
+  <si>
+    <t>Byzantinisches Reich</t>
+  </si>
+  <si>
+    <t>Mongolisches Reich</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Als Perserreich oder Persisches Reich wird das Großreich der Perser bezeichnet, das zeitweise von Thrakien bis nach Nordwestindien und Ägypten reichte. Es bestand in unterschiedlicher Ausdehnung von etwa 550 bis 330 v.u.Z. (Altpersisches Reich der Achämeniden) und von ca. 224 bis 651 n.u.Z. (Neupersisches Reich der Sassaniden). Das namensgebende Kernland des Perserreiches war die Persis (altpersisch </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Parsa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>), eine Region in Südwest-Iran. Von Vampir Clans der Zweiten Generation gegründet, hatte dieses Reich mit 
+Kämpfen gegen andere Urvölker und Hexenwesen zu kämpfen, die schlussendlich mit Völkerbewegung 
+zum Untergang des Reiches führten. Häuser der Clans zogen sich in den Norden Sibiriens zurück.</t>
+    </r>
+  </si>
+  <si>
+    <t>Das Byzantinische Reich war die unmittelbare Fortsetzung des Römischen Reiches im östlichen 
+Mittelmeerraum. Das Reich ging aus der Reichsteilung von 395 hervor und existierte bis zur Eroberung 
+Konstantinopels durch die Osmanen im Jahr 1453, womit es den Untergang Westroms um fast 1000 Jahre 
+überdauerte. In ihrem Einflussbereich konnten die Werwölfclans ihr Wissen weiter ausarbeiten.</t>
+  </si>
+  <si>
+    <t>Völkerwanderung und Verschwinden der Urvölker</t>
+  </si>
+  <si>
+    <t>Inkareich</t>
+  </si>
+  <si>
+    <t>Amerika</t>
+  </si>
+  <si>
+    <t>Das Mongolische Reich war das im 13. und 14. Jahrhundert von den vereinigten mongolischen Volksstämmen
+eroberte Territorium in Asien und Osteuropa und auf seinem Höhepunkt der größte zusammenhängende 
+Herrschaftsbereich der Weltgeschichte. Bei ihren Eroberungszügen bekamen die Clans erste Berührungen
+mit den Urvölkern und bauten So eine langandauernde Schattengesellschaft auf.</t>
+  </si>
+  <si>
+    <t>Das Inkareich war das größte Reich im präkolumbischen Amerika. Das administrative, politische und 
+militärische Zentrum des Reiches befand sich in der Stadt Cusco im heutigen Peru. Die Zivilisation der Inka
+entstand im frühen 13. Jahrhundert im Hochland der Anden. Von neuen Urvölkerclans gegründet wurde es durch die weiterfahreneren Vampirclans zerschlagen.</t>
+  </si>
+  <si>
+    <t>Völkerwanderung und Erscheinen der Vampire</t>
+  </si>
+  <si>
+    <t>Man besiegt Pucca, indem man ihre Supergeschwindigkeit kontert und sie mit gleichwertigen oder überlegenen Fähigkeiten bekämpft.</t>
+  </si>
+  <si>
+    <t>Um Sirenen zu besiegen, muss man je nach Kontext zwischen dem Schutz
+bei einem zivilen Sirenenalarm und dem Kampf gegen mythologische
+Sirenen oder Gegner in Videospielen unterscheiden. Bei einem Sirenenalarm
+sucht man geschlossene Räume auf, schaltet Lüftungen aus und informiert
+sich über Radio, Apps oder die Internetseite der Stadt. Im mythologischen
+Kontext war ein Weg, Sirenen zu entkommen, Odysseus, indem er seine
+Crew mit Wachs die Ohren versiegelte, während er selbst an den Mast
+gefesselt wurde.</t>
+  </si>
+  <si>
+    <t>Als Sperre gegen ihren Blutdurst wurden sie mit einer Abneigung 
+Sonnenlicht ausgestattet, bei der Sie zu Staub zerfallen belegt.</t>
+  </si>
+  <si>
+    <t>1.000 u.Z.: Durch dunke Magie kommt es zur Erschaffung von Urvampiren durch eine Hexe aus Skandinavien, um ihre Nachkommen vor Werwölfen zu beschützen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.000 u.Z.: Durch dunke Magie kommt es zur Erschaffung von Urvampiren durch eine Hexe aus Sibirien, um Rache an ihren Verfolgern zu nehmen. </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Doggerland
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>untergegangen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 
+&gt; Heute Mittelmeer</t>
+    </r>
+  </si>
+  <si>
+    <t>Nur noch wenige in Europa 
+übrig, in Griechenland ist eine gut aufgebaute Gemeinschaft</t>
+  </si>
+  <si>
+    <t>10.500 v.u.Z.: Das unbekannte hochentwickelte Volk was die ersten Urvampire erschuf, erlang die Macht
+andere Werwesen zu erschaffen. Als Unterstützung für die Tiere der Lüfte erschuf man verschiedene Clans.</t>
+  </si>
+  <si>
+    <t>In Mitteleuropa sind mehrere
+Gemeinschaften der Feen, 
+weltweit mehrere der anderen der anderen Clans.</t>
+  </si>
+  <si>
+    <t>10.500 v.u.Z.: Das unbekannte hochentwickelte Volk was die ersten Urvampire erschuf, erlang die Macht
+andere Werwesen zu erschaffen. Als Unterstützung für die Tiere der Meere erschuf man verschiedene Clans.</t>
+  </si>
+  <si>
+    <t>Um zum Beispiel Elfen zu besiegen, muss man oft ihre Stärken ausnutzen 
+und Schwächen ausspielen. Man kann sie im Nahkampf zwingen, wenn sie sich auf Fernkampf spezialisiert haben, oder sie aus der Entfernung angreifen, wenn sie eine schlechte Verteidigung haben. Da es verschiedene Arten von Elfen gibt, hängt die beste Strategie vom spezifischen Kontext ab.</t>
+  </si>
+  <si>
+    <t>Um zum Beispiel Meerjungfrauen zu besiegen, muss man sie durch Dehydrierung oder durch das Abwenden der Magie, sie zu schwächen. Man kann versuchen, die Umgebung zu ändern, um Meerjungfrauen zu schwächen, indem man sie aus dem Wasser lockt oder sie in etwas einschließt, das sie nicht vertragen können. Wenn Sie gegen eine Meerjungfrau kämpfen, recherchieren Sie die spezifischen Regeln und Schwächen, die für diese Situation gelten.</t>
+  </si>
+  <si>
+    <t>An Küsten, in Flüßen und Seen sind mehrere Gemeinschaften der Meerjungfrauen, weltweit mehrere der anderen der anderen Clans.</t>
+  </si>
+  <si>
+    <t>10.500 v.u.Z.: Das unbekannte hochentwickelte Volk was die ersten Urvampire erschuf, erlang die Macht
+andere Werwesen zu erschaffen. Als Unterstützung für die Tiere der Berge erschuf man verschiedene Clans.</t>
+  </si>
+  <si>
+    <t>Die Púca (Werziege)</t>
+  </si>
+  <si>
+    <t>Um einen Leprechaun zu besiegen, können Sie ihn mit Eisen neutralisieren, 
+was seine Magie schwächt und ihn töten kann. Eine weitere Möglichkeit ist 
+die Verwendung eines vierblättrigen Kleeblatts, das ihn aufhalten kann. 
+Alternativ kann man versuchen, ihn zu fangen und zu verhandeln, da 
+Leprechauns extrem geizig sind und ihr Gold nur ungern hergeben.</t>
+  </si>
+  <si>
+    <t>In Gebirgen findete man 
+mehrere Mitglieder 
+unterschiedlichster Werclans, 
+die sich in gutfunktionierenden Gemeinschaften gefunden haben.</t>
+  </si>
+  <si>
+    <t>11.000 v.u.Z.: Eine unbekannte hochentwickelte Spezies, verwandelt nach einem Angriff eines feindlichen Reiches, einen Teil ihrer Krieger in Monster mit Kräften, die Sie ihnen mit Hilfe von Meteoritengestein weitergaben. Aus einen Teil der Krieger entstanden die ersten Vampire. Die ihre Sinne und Agilität verbesserte und weitere Kräfte freischalteten.</t>
+  </si>
+  <si>
+    <t>11.000 v.u.Z.: Eine unbekannte hochentwickelte Spezies, verwandelt nach einem Angriff eines feindlichen
+Reiches, einen Teil ihrer Krieger in Monster mit Kräften, die Sie ihnen mit Hilfe von Meteoritengestein weitergaben. Ein kleiner Teil der Krieger verwandelte sich exponentiell und wurde zu den ersten Drachen.
+Diese wurden daraufhin als Reittiere für den Kampf benutzt und entwickelten besondere Kräfte.</t>
+  </si>
+  <si>
+    <t>Um einen Drachen zu besiegen, gibt es verschiedene Strategien, die je nach 
+Kontext variieren. Oft wird der Waffengang mit Schwertern und Speeren 
+genutzt. Auch Strategien wie das Zerstören von Heilkristallen mit einem 
+Bogen, der Einsatz von Nahkampfwaffen, wenn der Drache landet, und das
+Ausweichen benutzbar. Generell ist eine gute Rüstung, genügend Verpflegung
+und eine kluge Taktik entscheidend.</t>
+  </si>
+  <si>
+    <t>Nur noch wenige in Europa 
+übrig, auf den Balkan haben sich mehrere kleine Gemeinschaften aufgebaut, die sich auch zu ihren menschlichen Ursprung wandeln können.</t>
+  </si>
+  <si>
+    <t>Um Wassermagier ist dehydrieren der Umgebung aber auch Elektroschocks 
+sehr zu empfehlen. Wen man gegen Magier kämpf sollte man aber recherchieren welche sozialen oder körperlichen Schwächen haben, um ein positive Lösung der Misssionssitualtion zu erwirken.</t>
+  </si>
+  <si>
+    <t>In dieser Generation pflanzten 
+man sich durch Paarung fort.</t>
+  </si>
+  <si>
+    <t>Um einen Erdmagier zu besiegen, sollten Sie sich auf Fernkampfangriffe
+konzentrieren und seine Angriffe mit Ausweichen oder Blöcken kontern.</t>
+  </si>
+  <si>
+    <t>Erdmagier können mithilfe der Macht der Erde ihre Gruppen Heilen, aber auch um hnen den Weg zu ebnen und ihre Bewegung dadurch vereinfachen. Aber die Erdmagie ist nicht nur eine defensive Elementarmagie. Erdmagier können riesige Felsbrocken heraufbeschwören und damit ihren Feinden schweren Schaden zufügen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Windmagier sind Meister darin, Luftströmungen zu manipulieren und geschickt darin, andere Verbündete zu unterstützen und den Zorn der Gegner zu nutzen. Sie können mit Leichtigkeit das Schlachtfeld überqueren und aus unerwarteter Richtung und von den entlegensten Winkeln des Schlachtfeldes aus Zauber wirken und sind so die ideale Wahl für einen Truppengeneral, der ein wenig Magie zur rechten Zeit am rechten Ort benötigt. </t>
+  </si>
+  <si>
+    <t>Wassermagier können mithilfe von Wellen, Strömungen, Geysiren und Wasserstrahlen schwere stumpfe 
+Traumata verursachen . Durch die Erzeugung von Strudeln, Wasserhosen und Wirbeln kann ein Wassermagier 
+aufgrund der Kreiselkraft und der Schneidkraft verheerende Schäden verursachen. Auch können Sie das Blut 
+des eigenen Körpers manipulieren.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Um einen Windmagier zu besiegen, müssen Sie je anch Ziel die Schwächen des Gegners ausnutzen.  Oft werden Bomben in einen erzeugten Wirbelsturm geworfen, um ihn zu verkleinern, und dann Pfeile in das Auge des Magiers schießen, nachdem er zu Boden gefallen ist. </t>
+  </si>
+  <si>
+    <t>In dieser Generation pflanzt 
+man sich durch Paarung fort.</t>
+  </si>
+  <si>
+    <t>Um Feuermagier zu besiegen, ist es am besten,
+Eisangriffe zu verwenden, die gegen sie sehr effektiv sind, wie im Fall des Feuer-Pyromagus in Zelda: Breath of the Wild. Bei einem Kampf gegen einen Magier-Gegner kann es auch hilfreich sein, einen anderen Magier oder eine Fernkampf-Fähigkeit einzusetzen, damit diese sich gegenseitig angreifen, um sich einen Vorteil zu verschaffen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ein Feuermagier ist eine spezialisierte Magierklasse, die sich auf die Beherrschung von Elementen des Feuers konzentriert. Je nach Mission kann dies eine spezifische Rolle sein, bei der es um offensive Fähigkeiten geht, oder eine Priesterkaste, geht die mit Überresten von Urvölkern alte Götter anbetet. </t>
+  </si>
+  <si>
+    <t>Um einen Avatar zu besiegen, sollten Sie sich auf gut aufgebaute Ausrüstung
+konzentrieren und seine Angriffe mit Ausweichen oder Blöcken kontern.</t>
+  </si>
+  <si>
+    <t>In dieser Generation pflanzt 
+man sich nur einmal im Leben fort.</t>
+  </si>
+  <si>
+    <t>Avatare haben die Macht die Kräfte des Magischen Kosmos zu kontrollieren und Sie gegen sämtliche Gegner
+einzusetzen.</t>
+  </si>
+  <si>
+    <t>Ein Grüner Magier ist eine spezialisierte Magierklasse der Erdmagier, die sich auf die Beherrschung von Elementen der Natur konzentrieren. Je nach Mission kann dies die Umgebung verändern, das Verdauungsmaterial des Körpers aber auch die Magie anderer Magierclans.</t>
+  </si>
+  <si>
+    <t>Um einen Grünen Magier zu besiegen, sollte man eine große Mischung an Tränken
+mit sich führen und die Fähigkeiten entsprechend aufzubauen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die Magie des Lichts hat viele praktische Anwendungen, nutzt vor allem jedoch ihre Kräfte zur Heilung und zum
+Schutz. Doch auch blendende Blitze und gleißendes Licht, das den Feind verbrennt, sind ein Teil der Magie, der
+in dieser Form in erschaffenen Konstruktionen fokussiert werden kann. </t>
+  </si>
+  <si>
+    <t>Um einen Lichtmagier zu besiegen, sollten Sie eine gut vorbereitete, schlagkräftige und hochstufige Truppe mit einem ausgewogenen Verhältnis von Angriff und Verteidigung aufstellen. In der Regel ist es sinnvoll, die Charaktere zu erwecken, um nützliche Zusatzfähigkeiten zu erhalten, die den Schaden erhöhen. Die Auswahl der richtigen Ausrüstung wie Runen-Sets mit Set-Effekten, die Angriff- und Verteidigungs-Boosts bieten, ist ebenfalls entscheidend, da der Boss-Lichtmagier oft hohen Schaden verursacht</t>
+  </si>
+  <si>
+    <t>Um einen schwarzen Magier zu besiegen, hängt die Strategie davon ab, in welcher Umgebung man sich befindet. In Katakomben kann man zum Beispiel die Umgebung nutzen, den Magier zu Schwächen. Auch das nutzen von Lichtfähigkeiten kann die Kraft des Magiers beeinträchtigen.</t>
+  </si>
+  <si>
+    <t>Die Magie der Finsternis hat viele praktische Anwendungen, nutzt vor allem jedoch ihre Kräfte um andere Objekte und Lebensformen zu kontrollieren oder zu verletzen. Doch auch Schattenwesen und die Dunkelheit, das den Feind orrientierungslos macht.</t>
+  </si>
+  <si>
+    <t>Die Schwarzmagier</t>
+  </si>
+  <si>
+    <t>Die Lichtmagier</t>
+  </si>
+  <si>
+    <t>Lichtmagier können nur in
+Jahrelangen Studium der
+Lehren diese Art der Magie
+freigeschaltet werden</t>
+  </si>
+  <si>
+    <t>Schwarzmagier können nur in
+Jahrelangen Studium der
+Lehren diese Art der Magie
+freigeschaltet werden</t>
+  </si>
+  <si>
+    <t>Ein Zeitmagier ist sehr schwer zu besiegen, am besten durch einen Verbündeten Zeitmagier. Ein Kampf ist sehr gefährlich</t>
+  </si>
+  <si>
+    <t>Zeitmagier können nur in
+Jahrelangen Studium der
+Lehren und mehreren anderen Regeln (Nahtoferfahrung)
+freigeschaltet werden</t>
+  </si>
+  <si>
+    <t>Technomagier</t>
+  </si>
+  <si>
+    <t>Die Technomagier sind eine Neue Gruppierung der Magier die Technologie der Modernen Feld und die Energien
+der Moderne manipulieren und damit kämpfen können.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Klimawandel &gt; Sintflut</t>
+  </si>
+  <si>
+    <t>Klilmawandel &gt; Sintflut im Ostbereich</t>
+  </si>
+  <si>
+    <t>In dieser Generation pflanzten 
+man sich durch Bluttransfer 
+fort.</t>
+  </si>
+  <si>
+    <t>In dieser Generation kann es 
+zu keiner Fortpflanzung kommen.</t>
+  </si>
+  <si>
     <t>Damit der Werwolf gebremst werden kann, errang man ihn einen tödliche
-Anfälligkeit gegen Silber zu übertragen-</t>
-  </si>
-  <si>
-    <t>Als Sperre gegen ihren Blutdurst wurden sie mit einer Abneigung Sonnenlicht ausgestattet, bei der Sie zu Staub zerfallen belegt.</t>
-  </si>
-  <si>
-    <t>Sammelobjekte in Dhampir</t>
+Anfälligkeit gegen Silber zu übertragen.</t>
+  </si>
+  <si>
+    <t>Es sind mehrere 
+Gemeinschaften
+weltweit vorhanden.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.000 u.Z.: Durch dunke Magie kam es zur Erschaffung der ersten Sirenen, damit diese die Reiche vor den Werwesen der Meere beschützen. </t>
+  </si>
+  <si>
+    <t>Der Zeitmagier ist eine besonderer Magier und verfügt über die Gabe der Zeitmanipulation. Er kann die Kämpfe insofern beeinflussen, als dass er sowohl bei Freund wie Feind die Geschwindigkeit drosseln oder erhöhen kann. Auch kann er Portale in die Vergangenheit öffnen um verschwundene Fähigkeiten zu erlernen.</t>
+  </si>
+  <si>
+    <t>Die Technomagier sind eine 
+sehr neue Magiegruppe und 
+pflanzen Sich durchs Wissensvermittlung fort.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -333,6 +755,13 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -342,7 +771,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -535,19 +964,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thick">
         <color auto="1"/>
       </left>
@@ -621,20 +1037,20 @@
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
       <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -643,7 +1059,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -663,139 +1079,160 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="46" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="46" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="46" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="46" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="46" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="46" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="46" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1078,561 +1515,777 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:I77"/>
+  <dimension ref="A2:I78"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="35.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="92" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="64.42578125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="27.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="95.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="70.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="24.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="33" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
+      <c r="A2" s="46" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="45.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" s="23"/>
+      <c r="E5" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="H5" s="24"/>
+    </row>
+    <row r="6" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A6" s="33"/>
+      <c r="B6" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="9"/>
+      <c r="E6" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H6" s="6"/>
+    </row>
+    <row r="7" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="33"/>
+      <c r="B7" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="9"/>
+      <c r="E7" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="F7" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="H7" s="6"/>
+    </row>
+    <row r="8" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" s="33"/>
+      <c r="B8" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="9"/>
+      <c r="E8" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H8" s="6"/>
+    </row>
+    <row r="9" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="A9" s="33"/>
+      <c r="B9" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="28"/>
+      <c r="E9" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="F9" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="H9" s="29"/>
+    </row>
+    <row r="10" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A10" s="33"/>
+      <c r="B10" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="9"/>
+      <c r="E10" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G10" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" s="6"/>
+    </row>
+    <row r="11" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" s="33"/>
+      <c r="B11" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="9"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G11" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="H11" s="6"/>
+    </row>
+    <row r="12" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="33"/>
+      <c r="B12" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="28"/>
+      <c r="E12" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="G12" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" s="29"/>
+    </row>
+    <row r="13" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D13" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="60.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="19"/>
+      <c r="E14" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="33"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="9"/>
+      <c r="E15" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" s="38"/>
+      <c r="I15" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="33"/>
+      <c r="B16" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="9"/>
+      <c r="E16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" s="38" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="33"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="9"/>
+      <c r="E17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="41"/>
+      <c r="H17" s="40"/>
+    </row>
+    <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="33"/>
+      <c r="B18" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="9"/>
+      <c r="E18" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="G18" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="H18" s="38" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="33"/>
+      <c r="B19" s="37"/>
+      <c r="C19" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="28"/>
+      <c r="E19" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="G19" s="43"/>
+      <c r="H19" s="39"/>
+    </row>
+    <row r="20" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="33"/>
+      <c r="B20" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="26"/>
+      <c r="E20" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="G20" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="H20" s="57" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A21" s="33"/>
+      <c r="B21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="47" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="G21" s="47" t="s">
+        <v>54</v>
+      </c>
+      <c r="H21" s="48" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="33"/>
+      <c r="B22" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+      <c r="A23" s="33"/>
+      <c r="B23" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="47" t="s">
+        <v>86</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H23" s="48" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A24" s="33"/>
+      <c r="B24" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H24" s="53" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="A25" s="33"/>
+      <c r="B25" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" s="47" t="s">
+        <v>90</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H25" s="53" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="A26" s="33"/>
+      <c r="B26" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="54" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H26" s="53" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="34"/>
+      <c r="B27" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="F27" s="51" t="s">
+        <v>99</v>
+      </c>
+      <c r="G27" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="H27" s="48" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="75.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="45.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="28"/>
-      <c r="E5" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="29"/>
-      <c r="B6" s="30"/>
-      <c r="C6" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="11" t="s">
+      <c r="B29" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="14"/>
-      <c r="I6" s="1" t="s">
+      <c r="C29" s="23"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="54" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="29"/>
-      <c r="B7" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="29"/>
-      <c r="B8" s="30"/>
-      <c r="C8" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="17"/>
-      <c r="H8" s="19"/>
-    </row>
-    <row r="9" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="29"/>
-      <c r="B9" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="H9" s="14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="29"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="43"/>
-      <c r="E10" s="42" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="48" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" s="49"/>
-      <c r="H10" s="50"/>
-    </row>
-    <row r="11" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="29"/>
-      <c r="B11" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="51" t="s">
-        <v>65</v>
-      </c>
-      <c r="G11" s="51" t="s">
-        <v>66</v>
-      </c>
-      <c r="H11" s="41"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="29"/>
-      <c r="B12" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="25" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="29"/>
-      <c r="B13" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="6"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="29"/>
-      <c r="B14" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="6"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="29"/>
-      <c r="B15" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="29"/>
-      <c r="B16" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="6"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="29"/>
-      <c r="B17" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="6"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="29"/>
-      <c r="B18" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="6"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="29"/>
-      <c r="B19" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="6"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="29"/>
-      <c r="B20" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="6"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="29"/>
-      <c r="B21" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="6"/>
-    </row>
-    <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="31"/>
-      <c r="B22" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="34"/>
-    </row>
-    <row r="23" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="B23" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="F23" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="G23" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="H23" s="16" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="37"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="36"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="38"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="29"/>
-      <c r="B25" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="6"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="29"/>
-      <c r="B26" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="6"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="29"/>
-      <c r="B27" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="6"/>
-    </row>
-    <row r="28" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="29"/>
-      <c r="B28" s="32" t="s">
-        <v>52</v>
-      </c>
-      <c r="C28" s="33"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="34"/>
-    </row>
-    <row r="29" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="29"/>
-      <c r="B29" s="39" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29" s="40"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="39"/>
-      <c r="H29" s="41"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="29"/>
-      <c r="B30" s="3" t="s">
-        <v>59</v>
+      <c r="F29" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="G29" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="H29" s="56" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="A30" s="33"/>
+      <c r="B30" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="25"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="29"/>
+      <c r="E30" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="G30" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="H30" s="53" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A31" s="33"/>
       <c r="B31" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="6"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="29"/>
+        <v>33</v>
+      </c>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="54" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="H31" s="53" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A32" s="33"/>
       <c r="B32" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="6"/>
-    </row>
-    <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="29"/>
-      <c r="B33" s="42" t="s">
-        <v>55</v>
-      </c>
-      <c r="C33" s="43"/>
-      <c r="D33" s="43"/>
-      <c r="E33" s="42"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="42"/>
-      <c r="H33" s="44"/>
-    </row>
-    <row r="34" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="29"/>
-      <c r="B34" s="39" t="s">
-        <v>57</v>
-      </c>
-      <c r="C34" s="40"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="39"/>
-      <c r="H34" s="41"/>
-    </row>
-    <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="29"/>
-      <c r="B35" s="39" t="s">
-        <v>58</v>
-      </c>
-      <c r="C35" s="40"/>
-      <c r="D35" s="40"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="39"/>
-      <c r="H35" s="41"/>
-    </row>
-    <row r="36" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="29"/>
-      <c r="B36" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="C36" s="40"/>
-      <c r="D36" s="40"/>
-      <c r="E36" s="39"/>
-      <c r="F36" s="39"/>
-      <c r="G36" s="39"/>
-      <c r="H36" s="41"/>
-    </row>
-    <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="31"/>
-      <c r="B37" s="45" t="s">
-        <v>61</v>
-      </c>
-      <c r="C37" s="46"/>
-      <c r="D37" s="46"/>
-      <c r="E37" s="45"/>
-      <c r="F37" s="45"/>
-      <c r="G37" s="45"/>
-      <c r="H37" s="47"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="2"/>
-      <c r="B38" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="25"/>
+        <v>34</v>
+      </c>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="H32" s="53" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="33"/>
+      <c r="B33" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="F33" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="G33" s="51" t="s">
+        <v>112</v>
+      </c>
+      <c r="H33" s="53" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="33"/>
+      <c r="B34" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="G34" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="H34" s="57" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+      <c r="A35" s="33"/>
+      <c r="B35" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="47" t="s">
+        <v>117</v>
+      </c>
+      <c r="G35" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="H35" s="48" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A36" s="33"/>
+      <c r="B36" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="54" t="s">
+        <v>22</v>
+      </c>
+      <c r="F36" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="H36" s="48" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="33"/>
+      <c r="B37" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="F37" s="54" t="s">
+        <v>137</v>
+      </c>
+      <c r="G37" s="52" t="s">
+        <v>125</v>
+      </c>
+      <c r="H37" s="58" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="34"/>
+      <c r="B38" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C38" s="26"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="F38" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="G38" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="H38" s="57" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="4"/>
-      <c r="B39" s="5"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="6"/>
+      <c r="A39" s="2"/>
+      <c r="B39" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="18"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
       <c r="B40" s="5"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
@@ -1641,8 +2294,8 @@
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
       <c r="B41" s="5"/>
-      <c r="C41" s="10"/>
-      <c r="D41" s="10"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
@@ -1651,8 +2304,8 @@
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
       <c r="B42" s="5"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
@@ -1661,8 +2314,8 @@
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="4"/>
       <c r="B43" s="5"/>
-      <c r="C43" s="10"/>
-      <c r="D43" s="10"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
@@ -1671,8 +2324,8 @@
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="4"/>
       <c r="B44" s="5"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="10"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
@@ -1681,8 +2334,8 @@
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="4"/>
       <c r="B45" s="5"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="10"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
@@ -1691,8 +2344,8 @@
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
       <c r="B46" s="5"/>
-      <c r="C46" s="10"/>
-      <c r="D46" s="10"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
@@ -1701,8 +2354,8 @@
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="4"/>
       <c r="B47" s="5"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="10"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
@@ -1711,8 +2364,8 @@
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
       <c r="B48" s="5"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="10"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
@@ -1721,8 +2374,8 @@
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="4"/>
       <c r="B49" s="5"/>
-      <c r="C49" s="10"/>
-      <c r="D49" s="10"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
@@ -1731,8 +2384,8 @@
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="4"/>
       <c r="B50" s="5"/>
-      <c r="C50" s="10"/>
-      <c r="D50" s="10"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
       <c r="E50" s="5"/>
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
@@ -1741,8 +2394,8 @@
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="4"/>
       <c r="B51" s="5"/>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
       <c r="E51" s="5"/>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
@@ -1751,8 +2404,8 @@
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="4"/>
       <c r="B52" s="5"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="10"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
@@ -1761,8 +2414,8 @@
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="4"/>
       <c r="B53" s="5"/>
-      <c r="C53" s="10"/>
-      <c r="D53" s="10"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
       <c r="E53" s="5"/>
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
@@ -1771,8 +2424,8 @@
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="4"/>
       <c r="B54" s="5"/>
-      <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
       <c r="E54" s="5"/>
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
@@ -1781,8 +2434,8 @@
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="4"/>
       <c r="B55" s="5"/>
-      <c r="C55" s="10"/>
-      <c r="D55" s="10"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9"/>
       <c r="E55" s="5"/>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
@@ -1791,8 +2444,8 @@
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="4"/>
       <c r="B56" s="5"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="10"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
       <c r="E56" s="5"/>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
@@ -1801,8 +2454,8 @@
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="4"/>
       <c r="B57" s="5"/>
-      <c r="C57" s="10"/>
-      <c r="D57" s="10"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
       <c r="E57" s="5"/>
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
@@ -1811,8 +2464,8 @@
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="4"/>
       <c r="B58" s="5"/>
-      <c r="C58" s="10"/>
-      <c r="D58" s="10"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
       <c r="E58" s="5"/>
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
@@ -1821,8 +2474,8 @@
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="4"/>
       <c r="B59" s="5"/>
-      <c r="C59" s="10"/>
-      <c r="D59" s="10"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
       <c r="E59" s="5"/>
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>
@@ -1831,8 +2484,8 @@
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="4"/>
       <c r="B60" s="5"/>
-      <c r="C60" s="10"/>
-      <c r="D60" s="10"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9"/>
       <c r="E60" s="5"/>
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
@@ -1841,8 +2494,8 @@
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="4"/>
       <c r="B61" s="5"/>
-      <c r="C61" s="10"/>
-      <c r="D61" s="10"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
       <c r="E61" s="5"/>
       <c r="F61" s="5"/>
       <c r="G61" s="5"/>
@@ -1851,8 +2504,8 @@
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="4"/>
       <c r="B62" s="5"/>
-      <c r="C62" s="10"/>
-      <c r="D62" s="10"/>
+      <c r="C62" s="9"/>
+      <c r="D62" s="9"/>
       <c r="E62" s="5"/>
       <c r="F62" s="5"/>
       <c r="G62" s="5"/>
@@ -1861,8 +2514,8 @@
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="4"/>
       <c r="B63" s="5"/>
-      <c r="C63" s="10"/>
-      <c r="D63" s="10"/>
+      <c r="C63" s="9"/>
+      <c r="D63" s="9"/>
       <c r="E63" s="5"/>
       <c r="F63" s="5"/>
       <c r="G63" s="5"/>
@@ -1871,8 +2524,8 @@
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="4"/>
       <c r="B64" s="5"/>
-      <c r="C64" s="10"/>
-      <c r="D64" s="10"/>
+      <c r="C64" s="9"/>
+      <c r="D64" s="9"/>
       <c r="E64" s="5"/>
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
@@ -1881,8 +2534,8 @@
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="4"/>
       <c r="B65" s="5"/>
-      <c r="C65" s="10"/>
-      <c r="D65" s="10"/>
+      <c r="C65" s="9"/>
+      <c r="D65" s="9"/>
       <c r="E65" s="5"/>
       <c r="F65" s="5"/>
       <c r="G65" s="5"/>
@@ -1891,8 +2544,8 @@
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="4"/>
       <c r="B66" s="5"/>
-      <c r="C66" s="10"/>
-      <c r="D66" s="10"/>
+      <c r="C66" s="9"/>
+      <c r="D66" s="9"/>
       <c r="E66" s="5"/>
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
@@ -1901,8 +2554,8 @@
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="4"/>
       <c r="B67" s="5"/>
-      <c r="C67" s="10"/>
-      <c r="D67" s="10"/>
+      <c r="C67" s="9"/>
+      <c r="D67" s="9"/>
       <c r="E67" s="5"/>
       <c r="F67" s="5"/>
       <c r="G67" s="5"/>
@@ -1911,8 +2564,8 @@
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="4"/>
       <c r="B68" s="5"/>
-      <c r="C68" s="10"/>
-      <c r="D68" s="10"/>
+      <c r="C68" s="9"/>
+      <c r="D68" s="9"/>
       <c r="E68" s="5"/>
       <c r="F68" s="5"/>
       <c r="G68" s="5"/>
@@ -1921,8 +2574,8 @@
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="4"/>
       <c r="B69" s="5"/>
-      <c r="C69" s="10"/>
-      <c r="D69" s="10"/>
+      <c r="C69" s="9"/>
+      <c r="D69" s="9"/>
       <c r="E69" s="5"/>
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
@@ -1931,8 +2584,8 @@
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="4"/>
       <c r="B70" s="5"/>
-      <c r="C70" s="10"/>
-      <c r="D70" s="10"/>
+      <c r="C70" s="9"/>
+      <c r="D70" s="9"/>
       <c r="E70" s="5"/>
       <c r="F70" s="5"/>
       <c r="G70" s="5"/>
@@ -1941,8 +2594,8 @@
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="4"/>
       <c r="B71" s="5"/>
-      <c r="C71" s="10"/>
-      <c r="D71" s="10"/>
+      <c r="C71" s="9"/>
+      <c r="D71" s="9"/>
       <c r="E71" s="5"/>
       <c r="F71" s="5"/>
       <c r="G71" s="5"/>
@@ -1951,8 +2604,8 @@
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="4"/>
       <c r="B72" s="5"/>
-      <c r="C72" s="10"/>
-      <c r="D72" s="10"/>
+      <c r="C72" s="9"/>
+      <c r="D72" s="9"/>
       <c r="E72" s="5"/>
       <c r="F72" s="5"/>
       <c r="G72" s="5"/>
@@ -1961,8 +2614,8 @@
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="4"/>
       <c r="B73" s="5"/>
-      <c r="C73" s="10"/>
-      <c r="D73" s="10"/>
+      <c r="C73" s="9"/>
+      <c r="D73" s="9"/>
       <c r="E73" s="5"/>
       <c r="F73" s="5"/>
       <c r="G73" s="5"/>
@@ -1971,8 +2624,8 @@
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="4"/>
       <c r="B74" s="5"/>
-      <c r="C74" s="10"/>
-      <c r="D74" s="10"/>
+      <c r="C74" s="9"/>
+      <c r="D74" s="9"/>
       <c r="E74" s="5"/>
       <c r="F74" s="5"/>
       <c r="G74" s="5"/>
@@ -1981,8 +2634,8 @@
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="4"/>
       <c r="B75" s="5"/>
-      <c r="C75" s="10"/>
-      <c r="D75" s="10"/>
+      <c r="C75" s="9"/>
+      <c r="D75" s="9"/>
       <c r="E75" s="5"/>
       <c r="F75" s="5"/>
       <c r="G75" s="5"/>
@@ -1991,8 +2644,8 @@
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="4"/>
       <c r="B76" s="5"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="10"/>
+      <c r="C76" s="9"/>
+      <c r="D76" s="9"/>
       <c r="E76" s="5"/>
       <c r="F76" s="5"/>
       <c r="G76" s="5"/>
@@ -2001,28 +2654,39 @@
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="4"/>
       <c r="B77" s="5"/>
-      <c r="C77" s="10"/>
-      <c r="D77" s="10"/>
+      <c r="C77" s="9"/>
+      <c r="D77" s="9"/>
       <c r="E77" s="5"/>
       <c r="F77" s="5"/>
       <c r="G77" s="5"/>
       <c r="H77" s="6"/>
     </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="4"/>
+      <c r="B78" s="5"/>
+      <c r="C78" s="9"/>
+      <c r="D78" s="9"/>
+      <c r="E78" s="5"/>
+      <c r="F78" s="5"/>
+      <c r="G78" s="5"/>
+      <c r="H78" s="6"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A5:A22"/>
-    <mergeCell ref="A24:A37"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="B7:B8"/>
+  <mergeCells count="12">
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A5:A12"/>
+    <mergeCell ref="A14:A27"/>
+    <mergeCell ref="A29:A38"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B16:B17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>